--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N20_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N20_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.54925123004958</v>
+        <v>6.751753324883058</v>
       </c>
       <c r="D2" t="n">
-        <v>26.77647253854506</v>
+        <v>4.351176787513573</v>
       </c>
       <c r="E2" t="n">
-        <v>13.39503982992787</v>
+        <v>2.176693972363279</v>
       </c>
       <c r="F2" t="n">
-        <v>8.137857214945793</v>
+        <v>1.322401797428691</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.79898987322333</v>
+        <v>3.217335854398792</v>
       </c>
       <c r="D3" t="n">
-        <v>20.02918631294792</v>
+        <v>3.254742775854037</v>
       </c>
       <c r="E3" t="n">
-        <v>13.39503982992787</v>
+        <v>2.176693972363279</v>
       </c>
       <c r="F3" t="n">
-        <v>8.137857214945793</v>
+        <v>1.322401797428691</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>2.051911948189116</v>
+        <v>0.3334356915807313</v>
       </c>
       <c r="D4" t="n">
-        <v>3.616784958864295</v>
+        <v>0.5877275558154479</v>
       </c>
       <c r="E4" t="n">
-        <v>13.39503982992787</v>
+        <v>2.176693972363279</v>
       </c>
       <c r="F4" t="n">
-        <v>8.137857214945793</v>
+        <v>1.322401797428691</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.18077733212247</v>
+        <v>2.141876316469901</v>
       </c>
       <c r="D5" t="n">
-        <v>13.14551696475991</v>
+        <v>2.136146506773486</v>
       </c>
       <c r="E5" t="n">
-        <v>13.39503982992787</v>
+        <v>2.176693972363279</v>
       </c>
       <c r="F5" t="n">
-        <v>8.137857214945793</v>
+        <v>1.322401797428691</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.89532800418554</v>
+        <v>4.370490800680151</v>
       </c>
       <c r="D6" t="n">
-        <v>25.51054678884532</v>
+        <v>4.145463853187365</v>
       </c>
       <c r="E6" t="n">
-        <v>13.39503982992787</v>
+        <v>2.176693972363279</v>
       </c>
       <c r="F6" t="n">
-        <v>8.137857214945793</v>
+        <v>1.322401797428691</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.265893338101933</v>
+        <v>0.8557076674415642</v>
       </c>
       <c r="D7" t="n">
-        <v>23.76779920635515</v>
+        <v>3.862267371032711</v>
       </c>
       <c r="E7" t="n">
-        <v>13.39503982992787</v>
+        <v>2.176693972363279</v>
       </c>
       <c r="F7" t="n">
-        <v>8.137857214945793</v>
+        <v>1.322401797428691</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
